--- a/output/result.xlsx
+++ b/output/result.xlsx
@@ -472,13 +472,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -501,10 +501,10 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
@@ -553,7 +553,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
         <v>7</v>
@@ -579,7 +579,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
         <v>9</v>
@@ -605,7 +605,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
@@ -631,7 +631,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
         <v>7</v>
@@ -657,7 +657,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
         <v>14</v>
@@ -683,7 +683,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
         <v>14</v>
@@ -709,7 +709,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
         <v>8</v>

--- a/output/result.xlsx
+++ b/output/result.xlsx
@@ -472,13 +472,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
@@ -657,7 +657,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
         <v>14</v>
@@ -709,7 +709,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
         <v>8</v>

--- a/output/result.xlsx
+++ b/output/result.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
         <v>11</v>
@@ -501,10 +501,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -579,10 +579,10 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -602,10 +602,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
@@ -683,10 +683,10 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
         <v>8</v>
@@ -732,10 +732,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
         <v>8</v>

--- a/output/result.xlsx
+++ b/output/result.xlsx
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
         <v>11</v>
@@ -527,7 +527,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
@@ -579,7 +579,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
         <v>8</v>
@@ -602,13 +602,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
         <v>7</v>
@@ -709,7 +709,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
         <v>8</v>
@@ -732,10 +732,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
         <v>8</v>
